--- a/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -369,7 +369,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -663,7 +663,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -862,7 +862,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitionerrole-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
